--- a/Results/Phase 2/Methanol/methanol land use results.xlsx
+++ b/Results/Phase 2/Methanol/methanol land use results.xlsx
@@ -3314,85 +3314,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.015130394435441</v>
+        <v>0.9878575996482915</v>
       </c>
       <c r="C33" t="n">
-        <v>1.033169447262261</v>
+        <v>1.006260196590367</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9864865089434348</v>
+        <v>0.9694451394929073</v>
       </c>
       <c r="E33" t="n">
-        <v>0.8943454498254475</v>
+        <v>0.9355739465382209</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9538606373326268</v>
+        <v>0.9503781085116454</v>
       </c>
       <c r="G33" t="n">
-        <v>1.229186994704397</v>
+        <v>1.117146623183071</v>
       </c>
       <c r="H33" t="n">
-        <v>1.016884034324578</v>
+        <v>0.9864263035179937</v>
       </c>
       <c r="I33" t="n">
-        <v>1.040406238652997</v>
+        <v>1.000579453980493</v>
       </c>
       <c r="J33" t="n">
-        <v>1.121297772669479</v>
+        <v>1.050871850627878</v>
       </c>
       <c r="K33" t="n">
-        <v>1.176690463439268</v>
+        <v>1.080588987298926</v>
       </c>
       <c r="L33" t="n">
-        <v>0.9897049756147419</v>
+        <v>0.9718571930885381</v>
       </c>
       <c r="M33" t="n">
-        <v>1.325161621274137</v>
+        <v>1.165445599190686</v>
       </c>
       <c r="N33" t="n">
-        <v>1.062154001714374</v>
+        <v>1.014253371578842</v>
       </c>
       <c r="O33" t="n">
-        <v>2.922944841214739</v>
+        <v>2.862668327866937</v>
       </c>
       <c r="P33" t="n">
-        <v>1.091581300575481</v>
+        <v>1.034258973883992</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.002523695810375</v>
+        <v>0.9790162036166166</v>
       </c>
       <c r="R33" t="n">
-        <v>1.065567520872047</v>
+        <v>1.014798107769273</v>
       </c>
       <c r="S33" t="n">
-        <v>1.126675314851784</v>
+        <v>1.054926633933857</v>
       </c>
       <c r="T33" t="n">
-        <v>1.04462190669048</v>
+        <v>1.003193412833168</v>
       </c>
       <c r="U33" t="n">
-        <v>1.155386606474484</v>
+        <v>1.089686297538325</v>
       </c>
       <c r="V33" t="n">
-        <v>1.090627342358477</v>
+        <v>1.033815190229272</v>
       </c>
       <c r="W33" t="n">
-        <v>1.190439119121693</v>
+        <v>1.151996550463992</v>
       </c>
       <c r="X33" t="n">
-        <v>1.011323632677805</v>
+        <v>0.9840529275391154</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.047707248745153</v>
+        <v>1.006094391944768</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.8172867950492985</v>
+        <v>0.783393166373124</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.126263411045683</v>
+        <v>1.052519787703579</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.313845162905652</v>
+        <v>1.156228382138937</v>
       </c>
     </row>
   </sheetData>
@@ -6286,85 +6286,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.70454747144609</v>
+        <v>1.585001090039449</v>
       </c>
       <c r="C33" t="n">
-        <v>2.127436521488108</v>
+        <v>1.96413454355268</v>
       </c>
       <c r="D33" t="n">
-        <v>1.680103672443047</v>
+        <v>1.564249789583609</v>
       </c>
       <c r="E33" t="n">
-        <v>1.640750171472973</v>
+        <v>1.52780326129016</v>
       </c>
       <c r="F33" t="n">
-        <v>1.991525197301743</v>
+        <v>1.746323203419439</v>
       </c>
       <c r="G33" t="n">
-        <v>1.554668093967661</v>
+        <v>1.493286467442678</v>
       </c>
       <c r="H33" t="n">
-        <v>1.492974625331103</v>
+        <v>1.451037405392648</v>
       </c>
       <c r="I33" t="n">
-        <v>1.725813229031692</v>
+        <v>1.588598666828565</v>
       </c>
       <c r="J33" t="n">
-        <v>1.637570457129785</v>
+        <v>1.541313128528041</v>
       </c>
       <c r="K33" t="n">
-        <v>1.69398061995174</v>
+        <v>1.577423669832567</v>
       </c>
       <c r="L33" t="n">
-        <v>1.909238473819359</v>
+        <v>1.711274243681842</v>
       </c>
       <c r="M33" t="n">
-        <v>1.557232032403886</v>
+        <v>1.49020278784285</v>
       </c>
       <c r="N33" t="n">
-        <v>1.595191090776441</v>
+        <v>1.512436742016317</v>
       </c>
       <c r="O33" t="n">
-        <v>4.368596244791631</v>
+        <v>4.326872467583322</v>
       </c>
       <c r="P33" t="n">
-        <v>1.543153723657129</v>
+        <v>1.486022772917093</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.758116281799436</v>
+        <v>1.613579756135519</v>
       </c>
       <c r="R33" t="n">
-        <v>2.414864072036832</v>
+        <v>1.985930375159933</v>
       </c>
       <c r="S33" t="n">
-        <v>1.805758882661574</v>
+        <v>1.648624888936</v>
       </c>
       <c r="T33" t="n">
-        <v>1.601183187270107</v>
+        <v>1.515073934466822</v>
       </c>
       <c r="U33" t="n">
-        <v>2.572193839706354</v>
+        <v>2.522109415067867</v>
       </c>
       <c r="V33" t="n">
-        <v>1.606473845837513</v>
+        <v>1.525232443776126</v>
       </c>
       <c r="W33" t="n">
-        <v>2.963437374753027</v>
+        <v>2.851146054355597</v>
       </c>
       <c r="X33" t="n">
-        <v>1.670223137759857</v>
+        <v>1.559372743788682</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.61928866654798</v>
+        <v>1.527159939402545</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.022858285746695</v>
+        <v>1.937984091938359</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.591968434698568</v>
+        <v>1.5112407941934</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.639272067186518</v>
+        <v>1.535603186305307</v>
       </c>
     </row>
   </sheetData>
@@ -9258,85 +9258,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.125101899807856</v>
+        <v>1.097600731082314</v>
       </c>
       <c r="C33" t="n">
-        <v>1.181590696839326</v>
+        <v>1.148551977705432</v>
       </c>
       <c r="D33" t="n">
-        <v>1.158814882659546</v>
+        <v>1.115444902534887</v>
       </c>
       <c r="E33" t="n">
-        <v>1.067187772379421</v>
+        <v>1.075782088915268</v>
       </c>
       <c r="F33" t="n">
-        <v>1.054010069166955</v>
+        <v>1.054245576610481</v>
       </c>
       <c r="G33" t="n">
-        <v>1.414462321860424</v>
+        <v>1.273146449424577</v>
       </c>
       <c r="H33" t="n">
-        <v>1.096311212526723</v>
+        <v>1.078632288725679</v>
       </c>
       <c r="I33" t="n">
-        <v>1.190993237605889</v>
+        <v>1.133812908395185</v>
       </c>
       <c r="J33" t="n">
-        <v>1.274779689628525</v>
+        <v>1.187061308970235</v>
       </c>
       <c r="K33" t="n">
-        <v>1.25189330761804</v>
+        <v>1.172496387407399</v>
       </c>
       <c r="L33" t="n">
-        <v>1.103364259584447</v>
+        <v>1.083763527123905</v>
       </c>
       <c r="M33" t="n">
-        <v>1.404246379223002</v>
+        <v>1.257628614233145</v>
       </c>
       <c r="N33" t="n">
-        <v>1.173663141416817</v>
+        <v>1.124870364859851</v>
       </c>
       <c r="O33" t="n">
-        <v>3.191872596784353</v>
+        <v>3.134578017010664</v>
       </c>
       <c r="P33" t="n">
-        <v>1.233317342611412</v>
+        <v>1.163367212525334</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.13722444075969</v>
+        <v>1.103308134853242</v>
       </c>
       <c r="R33" t="n">
-        <v>1.13547706109307</v>
+        <v>1.101415260758076</v>
       </c>
       <c r="S33" t="n">
-        <v>1.252087454785205</v>
+        <v>1.174336994830418</v>
       </c>
       <c r="T33" t="n">
-        <v>1.166750861999922</v>
+        <v>1.120052538149341</v>
       </c>
       <c r="U33" t="n">
-        <v>1.521176654675485</v>
+        <v>1.450867505133</v>
       </c>
       <c r="V33" t="n">
-        <v>1.204721174932815</v>
+        <v>1.146975582351222</v>
       </c>
       <c r="W33" t="n">
-        <v>1.607361546539579</v>
+        <v>1.555353409625356</v>
       </c>
       <c r="X33" t="n">
-        <v>1.175688126308337</v>
+        <v>1.125692551839819</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.207351138811501</v>
+        <v>1.145550313955375</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.032745906492658</v>
+        <v>0.9855011740662635</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.184939653504904</v>
+        <v>1.132047849029088</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.422831367967313</v>
+        <v>1.265289267195875</v>
       </c>
     </row>
   </sheetData>
@@ -12230,85 +12230,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.317292385780281</v>
+        <v>1.27874381473922</v>
       </c>
       <c r="C33" t="n">
-        <v>1.508899572533561</v>
+        <v>1.462192092133094</v>
       </c>
       <c r="D33" t="n">
-        <v>1.384517229965764</v>
+        <v>1.315745779844434</v>
       </c>
       <c r="E33" t="n">
-        <v>1.276147887368253</v>
+        <v>1.251972806673008</v>
       </c>
       <c r="F33" t="n">
-        <v>1.308841207595711</v>
+        <v>1.271408967319445</v>
       </c>
       <c r="G33" t="n">
-        <v>1.589232962510819</v>
+        <v>1.445013792283227</v>
       </c>
       <c r="H33" t="n">
-        <v>1.259692565887997</v>
+        <v>1.242403525333958</v>
       </c>
       <c r="I33" t="n">
-        <v>1.693612772363445</v>
+        <v>1.494523083984643</v>
       </c>
       <c r="J33" t="n">
-        <v>1.463613667311979</v>
+        <v>1.366332415668347</v>
       </c>
       <c r="K33" t="n">
-        <v>1.416014637952702</v>
+        <v>1.338279458801908</v>
       </c>
       <c r="L33" t="n">
-        <v>1.277168296340413</v>
+        <v>1.253721009482685</v>
       </c>
       <c r="M33" t="n">
-        <v>1.566202468300054</v>
+        <v>1.420422561738919</v>
       </c>
       <c r="N33" t="n">
-        <v>1.359615443849179</v>
+        <v>1.301863761851932</v>
       </c>
       <c r="O33" t="n">
-        <v>3.78959954958707</v>
+        <v>3.733027240075947</v>
       </c>
       <c r="P33" t="n">
-        <v>1.403978446954244</v>
+        <v>1.331931252748823</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.55121941631441</v>
+        <v>1.416039127937536</v>
       </c>
       <c r="R33" t="n">
-        <v>1.282852905161654</v>
+        <v>1.255954087607616</v>
       </c>
       <c r="S33" t="n">
-        <v>1.421482487151313</v>
+        <v>1.342044163358167</v>
       </c>
       <c r="T33" t="n">
-        <v>1.314960269758232</v>
+        <v>1.274940566812461</v>
       </c>
       <c r="U33" t="n">
-        <v>2.016955910957317</v>
+        <v>1.965645542869658</v>
       </c>
       <c r="V33" t="n">
-        <v>1.368206414244428</v>
+        <v>1.31103559618376</v>
       </c>
       <c r="W33" t="n">
-        <v>2.227574817965085</v>
+        <v>2.16599706937464</v>
       </c>
       <c r="X33" t="n">
-        <v>1.373602090086842</v>
+        <v>1.309824523522165</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.479471113232923</v>
+        <v>1.373938218351318</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.453461471314019</v>
+        <v>1.387754940664718</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.344345263826244</v>
+        <v>1.293373396809063</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.574021685266611</v>
+        <v>1.42180276099447</v>
       </c>
     </row>
   </sheetData>
@@ -15202,85 +15202,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.430737573174457</v>
+        <v>1.3892058979122</v>
       </c>
       <c r="C33" t="n">
-        <v>1.64681888298712</v>
+        <v>1.622601059376612</v>
       </c>
       <c r="D33" t="n">
-        <v>1.466419972931135</v>
+        <v>1.407986086170108</v>
       </c>
       <c r="E33" t="n">
-        <v>1.296361537649988</v>
+        <v>1.292604547936756</v>
       </c>
       <c r="F33" t="n">
-        <v>1.482605751520766</v>
+        <v>1.416716260487955</v>
       </c>
       <c r="G33" t="n">
-        <v>1.675514669115318</v>
+        <v>1.540800219604039</v>
       </c>
       <c r="H33" t="n">
-        <v>1.376226212953235</v>
+        <v>1.353795833575107</v>
       </c>
       <c r="I33" t="n">
-        <v>1.656338970635027</v>
+        <v>1.517994355671373</v>
       </c>
       <c r="J33" t="n">
-        <v>1.564487444506536</v>
+        <v>1.469609440143095</v>
       </c>
       <c r="K33" t="n">
-        <v>1.537214530630029</v>
+        <v>1.452908406681985</v>
       </c>
       <c r="L33" t="n">
-        <v>1.419834912198366</v>
+        <v>1.381435941775241</v>
       </c>
       <c r="M33" t="n">
-        <v>1.640858535636771</v>
+        <v>1.510309143606958</v>
       </c>
       <c r="N33" t="n">
-        <v>1.461322289662347</v>
+        <v>1.404656001092628</v>
       </c>
       <c r="O33" t="n">
-        <v>4.179189787134325</v>
+        <v>4.125867574258414</v>
       </c>
       <c r="P33" t="n">
-        <v>1.51451386903334</v>
+        <v>1.441323020097556</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.551133180833673</v>
+        <v>1.459638660293076</v>
       </c>
       <c r="R33" t="n">
-        <v>1.559949264932514</v>
+        <v>1.459926503579849</v>
       </c>
       <c r="S33" t="n">
-        <v>1.54489169962672</v>
+        <v>1.458651822913533</v>
       </c>
       <c r="T33" t="n">
-        <v>1.498705456762273</v>
+        <v>1.425527033216894</v>
       </c>
       <c r="U33" t="n">
-        <v>2.361581913203563</v>
+        <v>2.318105546771791</v>
       </c>
       <c r="V33" t="n">
-        <v>1.49582384056162</v>
+        <v>1.430181402990503</v>
       </c>
       <c r="W33" t="n">
-        <v>2.641229419773342</v>
+        <v>2.572751734231557</v>
       </c>
       <c r="X33" t="n">
-        <v>1.520090461377085</v>
+        <v>1.44016894283027</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.73518780473915</v>
+        <v>1.566763762965354</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.757398238829821</v>
+        <v>1.690275400120646</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.472345340111389</v>
+        <v>1.411685769218787</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.677279066938845</v>
+        <v>1.52668057750969</v>
       </c>
     </row>
   </sheetData>
@@ -18174,85 +18174,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.344474752088626</v>
+        <v>1.296141378574807</v>
       </c>
       <c r="C33" t="n">
-        <v>1.651800639862785</v>
+        <v>1.578408860376195</v>
       </c>
       <c r="D33" t="n">
-        <v>1.297714834881586</v>
+        <v>1.265345666026739</v>
       </c>
       <c r="E33" t="n">
-        <v>1.80385586682897</v>
+        <v>1.570064771412605</v>
       </c>
       <c r="F33" t="n">
-        <v>1.570233619200258</v>
+        <v>1.425237715886495</v>
       </c>
       <c r="G33" t="n">
-        <v>1.397400775922034</v>
+        <v>1.330422913408286</v>
       </c>
       <c r="H33" t="n">
-        <v>1.364905117536042</v>
+        <v>1.303106133014717</v>
       </c>
       <c r="I33" t="n">
-        <v>1.548579337081183</v>
+        <v>1.411212347711989</v>
       </c>
       <c r="J33" t="n">
-        <v>1.418657123030377</v>
+        <v>1.341097034678186</v>
       </c>
       <c r="K33" t="n">
-        <v>1.555821093689049</v>
+        <v>1.423153201553168</v>
       </c>
       <c r="L33" t="n">
-        <v>1.825277343944681</v>
+        <v>1.59664971458515</v>
       </c>
       <c r="M33" t="n">
-        <v>1.43573590240033</v>
+        <v>1.349150205994277</v>
       </c>
       <c r="N33" t="n">
-        <v>1.40724653323655</v>
+        <v>1.331420966661215</v>
       </c>
       <c r="O33" t="n">
-        <v>3.942677801882108</v>
+        <v>3.914285401225499</v>
       </c>
       <c r="P33" t="n">
-        <v>1.340262892000988</v>
+        <v>1.29320221600866</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.516361758456278</v>
+        <v>1.397346722582237</v>
       </c>
       <c r="R33" t="n">
-        <v>1.579897579033823</v>
+        <v>1.427416392079204</v>
       </c>
       <c r="S33" t="n">
-        <v>1.615142599713106</v>
+        <v>1.471093490255702</v>
       </c>
       <c r="T33" t="n">
-        <v>1.360797212763036</v>
+        <v>1.303121562165529</v>
       </c>
       <c r="U33" t="n">
-        <v>2.020495910319197</v>
+        <v>1.978336431338139</v>
       </c>
       <c r="V33" t="n">
-        <v>1.359967282043422</v>
+        <v>1.305953024707091</v>
       </c>
       <c r="W33" t="n">
-        <v>2.262678631283577</v>
+        <v>2.203523661915008</v>
       </c>
       <c r="X33" t="n">
-        <v>1.523459065957665</v>
+        <v>1.398528806104107</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.328452302493621</v>
+        <v>1.284380197317984</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.551169278603272</v>
+        <v>1.48800867947475</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.30661239718744</v>
+        <v>1.27130613583877</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.355461013295947</v>
+        <v>1.298348883805905</v>
       </c>
     </row>
   </sheetData>
@@ -21146,85 +21146,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.070395039714633</v>
+        <v>1.823143699461177</v>
       </c>
       <c r="C33" t="n">
-        <v>2.098079873444882</v>
+        <v>1.957986529716214</v>
       </c>
       <c r="D33" t="n">
-        <v>1.504252073596022</v>
+        <v>1.475044817892879</v>
       </c>
       <c r="E33" t="n">
-        <v>2.592983343277147</v>
+        <v>2.116037493098442</v>
       </c>
       <c r="F33" t="n">
-        <v>2.206650039419258</v>
+        <v>1.891649188058916</v>
       </c>
       <c r="G33" t="n">
-        <v>1.57933227500526</v>
+        <v>1.5245725606712</v>
       </c>
       <c r="H33" t="n">
-        <v>1.621738699320604</v>
+        <v>1.541983371252289</v>
       </c>
       <c r="I33" t="n">
-        <v>1.994771960760812</v>
+        <v>1.763882661937012</v>
       </c>
       <c r="J33" t="n">
-        <v>1.737854181778337</v>
+        <v>1.619761392251513</v>
       </c>
       <c r="K33" t="n">
-        <v>1.744024105824439</v>
+        <v>1.622824542260659</v>
       </c>
       <c r="L33" t="n">
-        <v>1.938430901684336</v>
+        <v>1.75813167899383</v>
       </c>
       <c r="M33" t="n">
-        <v>1.580046272027826</v>
+        <v>1.522209447322722</v>
       </c>
       <c r="N33" t="n">
-        <v>1.817699511198066</v>
+        <v>1.664149383811716</v>
       </c>
       <c r="O33" t="n">
-        <v>4.77832940909955</v>
+        <v>4.639584258862036</v>
       </c>
       <c r="P33" t="n">
-        <v>1.565365634464314</v>
+        <v>1.514144471025773</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.775767377344676</v>
+        <v>1.644737362697924</v>
       </c>
       <c r="R33" t="n">
-        <v>2.27991323015464</v>
+        <v>1.927387335411227</v>
       </c>
       <c r="S33" t="n">
-        <v>1.842681224870441</v>
+        <v>1.692388327258496</v>
       </c>
       <c r="T33" t="n">
-        <v>1.669709103838184</v>
+        <v>1.574554725052664</v>
       </c>
       <c r="U33" t="n">
-        <v>2.626052549132298</v>
+        <v>2.585825086469658</v>
       </c>
       <c r="V33" t="n">
-        <v>1.676302243131937</v>
+        <v>1.584374201271563</v>
       </c>
       <c r="W33" t="n">
-        <v>3.084388303240258</v>
+        <v>2.960937025144788</v>
       </c>
       <c r="X33" t="n">
-        <v>1.753052391784165</v>
+        <v>1.625424645149035</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.595673431561466</v>
+        <v>1.52963469264904</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.405635309682713</v>
+        <v>2.229973015222973</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.548290786847639</v>
+        <v>1.501587786238241</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.584177765748495</v>
+        <v>1.521880186923126</v>
       </c>
     </row>
   </sheetData>
@@ -24118,85 +24118,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.500632175306245</v>
+        <v>2.121568942365168</v>
       </c>
       <c r="C33" t="n">
-        <v>2.363962732555741</v>
+        <v>2.167503157469588</v>
       </c>
       <c r="D33" t="n">
-        <v>1.899907945963978</v>
+        <v>1.74479915843678</v>
       </c>
       <c r="E33" t="n">
-        <v>2.553203451377792</v>
+        <v>2.133262449347846</v>
       </c>
       <c r="F33" t="n">
-        <v>2.134047105370057</v>
+        <v>1.879301817249551</v>
       </c>
       <c r="G33" t="n">
-        <v>1.71017405149636</v>
+        <v>1.636856028370553</v>
       </c>
       <c r="H33" t="n">
-        <v>1.646109850476192</v>
+        <v>1.591865065960915</v>
       </c>
       <c r="I33" t="n">
-        <v>1.815601143567558</v>
+        <v>1.692176738693051</v>
       </c>
       <c r="J33" t="n">
-        <v>1.824172536310106</v>
+        <v>1.704272527656931</v>
       </c>
       <c r="K33" t="n">
-        <v>1.722661407839304</v>
+        <v>1.640608787860942</v>
       </c>
       <c r="L33" t="n">
-        <v>1.958629529587022</v>
+        <v>1.794368444282183</v>
       </c>
       <c r="M33" t="n">
-        <v>1.634879884915971</v>
+        <v>1.586844736934375</v>
       </c>
       <c r="N33" t="n">
-        <v>1.797269923209507</v>
+        <v>1.68415393233951</v>
       </c>
       <c r="O33" t="n">
-        <v>5.001285932019964</v>
+        <v>4.860271844838035</v>
       </c>
       <c r="P33" t="n">
-        <v>1.702335147314748</v>
+        <v>1.631746645271719</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.919656924173378</v>
+        <v>1.760829566766565</v>
       </c>
       <c r="R33" t="n">
-        <v>2.520843090467557</v>
+        <v>2.100416521699823</v>
       </c>
       <c r="S33" t="n">
-        <v>1.895696586372267</v>
+        <v>1.751785977575304</v>
       </c>
       <c r="T33" t="n">
-        <v>1.674483629856127</v>
+        <v>1.610085213766424</v>
       </c>
       <c r="U33" t="n">
-        <v>2.899419578704545</v>
+        <v>2.856505714753016</v>
       </c>
       <c r="V33" t="n">
-        <v>1.798755450852335</v>
+        <v>1.691215430394734</v>
       </c>
       <c r="W33" t="n">
-        <v>3.440095738943606</v>
+        <v>3.289740322466352</v>
       </c>
       <c r="X33" t="n">
-        <v>1.831653448636553</v>
+        <v>1.707273708081606</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.737198006987961</v>
+        <v>1.647435967092193</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.527713764426289</v>
+        <v>2.366790122111535</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.652785729079247</v>
+        <v>1.597851427876703</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.729788148093694</v>
+        <v>1.640742053899868</v>
       </c>
     </row>
   </sheetData>
@@ -27090,85 +27090,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.267380408267295</v>
+        <v>1.205442522634071</v>
       </c>
       <c r="C33" t="n">
-        <v>1.319381549965888</v>
+        <v>1.255704497760726</v>
       </c>
       <c r="D33" t="n">
-        <v>1.172938151479179</v>
+        <v>1.145696762398985</v>
       </c>
       <c r="E33" t="n">
-        <v>1.466866341051104</v>
+        <v>1.334781007094896</v>
       </c>
       <c r="F33" t="n">
-        <v>1.388628681321497</v>
+        <v>1.271752040173054</v>
       </c>
       <c r="G33" t="n">
-        <v>1.466422499914014</v>
+        <v>1.328672112812603</v>
       </c>
       <c r="H33" t="n">
-        <v>1.189915135720963</v>
+        <v>1.154803028177891</v>
       </c>
       <c r="I33" t="n">
-        <v>1.482667665366785</v>
+        <v>1.325912642299349</v>
       </c>
       <c r="J33" t="n">
-        <v>1.360128468841029</v>
+        <v>1.260870092676334</v>
       </c>
       <c r="K33" t="n">
-        <v>1.485386742752126</v>
+        <v>1.336664939266625</v>
       </c>
       <c r="L33" t="n">
-        <v>1.350878041540426</v>
+        <v>1.254137658167027</v>
       </c>
       <c r="M33" t="n">
-        <v>1.551037798607242</v>
+        <v>1.372631242728733</v>
       </c>
       <c r="N33" t="n">
-        <v>1.283271442093739</v>
+        <v>1.211134260920225</v>
       </c>
       <c r="O33" t="n">
-        <v>3.277763970231672</v>
+        <v>3.23598755212623</v>
       </c>
       <c r="P33" t="n">
-        <v>1.271546068363263</v>
+        <v>1.20729449896981</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.383363301559339</v>
+        <v>1.27128405065122</v>
       </c>
       <c r="R33" t="n">
-        <v>1.396847310210031</v>
+        <v>1.274367385561157</v>
       </c>
       <c r="S33" t="n">
-        <v>1.428335335692121</v>
+        <v>1.306420484861177</v>
       </c>
       <c r="T33" t="n">
-        <v>1.270136629154942</v>
+        <v>1.202305985981476</v>
       </c>
       <c r="U33" t="n">
-        <v>1.658229507918017</v>
+        <v>1.600462529576784</v>
       </c>
       <c r="V33" t="n">
-        <v>1.239148402867072</v>
+        <v>1.188400267763289</v>
       </c>
       <c r="W33" t="n">
-        <v>1.759759093099394</v>
+        <v>1.718949424377585</v>
       </c>
       <c r="X33" t="n">
-        <v>1.396246991881499</v>
+        <v>1.276893604393205</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.263614289396004</v>
+        <v>1.200447600114641</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.145629129959614</v>
+        <v>1.106862793625694</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.225985645017015</v>
+        <v>1.177850363706972</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.432645933357289</v>
+        <v>1.29373183099983</v>
       </c>
     </row>
   </sheetData>
@@ -30062,85 +30062,85 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.633333767793792</v>
+        <v>1.505922257209746</v>
       </c>
       <c r="C33" t="n">
-        <v>1.989228320826358</v>
+        <v>1.824726293435056</v>
       </c>
       <c r="D33" t="n">
-        <v>1.504720478363273</v>
+        <v>1.422872044663596</v>
       </c>
       <c r="E33" t="n">
-        <v>1.89973769459603</v>
+        <v>1.656780870653005</v>
       </c>
       <c r="F33" t="n">
-        <v>1.926492132133684</v>
+        <v>1.671799825572542</v>
       </c>
       <c r="G33" t="n">
-        <v>1.629449846311989</v>
+        <v>1.507684591570853</v>
       </c>
       <c r="H33" t="n">
-        <v>1.382599822332379</v>
+        <v>1.349735006093896</v>
       </c>
       <c r="I33" t="n">
-        <v>1.757680225419188</v>
+        <v>1.568521874820648</v>
       </c>
       <c r="J33" t="n">
-        <v>1.593471311139489</v>
+        <v>1.481074719280266</v>
       </c>
       <c r="K33" t="n">
-        <v>1.691530799896964</v>
+        <v>1.541856794125502</v>
       </c>
       <c r="L33" t="n">
-        <v>1.925002861771146</v>
+        <v>1.687607963090602</v>
       </c>
       <c r="M33" t="n">
-        <v>1.508930327035339</v>
+        <v>1.427297863975838</v>
       </c>
       <c r="N33" t="n">
-        <v>1.498221930615585</v>
+        <v>1.419069603976278</v>
       </c>
       <c r="O33" t="n">
-        <v>4.076458096165788</v>
+        <v>4.041341083642894</v>
       </c>
       <c r="P33" t="n">
-        <v>1.471095046873833</v>
+        <v>1.406981666756114</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.736507786149834</v>
+        <v>1.568303389316237</v>
       </c>
       <c r="R33" t="n">
-        <v>1.972056802137341</v>
+        <v>1.690520397904336</v>
       </c>
       <c r="S33" t="n">
-        <v>1.769430364779478</v>
+        <v>1.594300252161804</v>
       </c>
       <c r="T33" t="n">
-        <v>1.594003032147811</v>
+        <v>1.474406672505601</v>
       </c>
       <c r="U33" t="n">
-        <v>2.248509667582235</v>
+        <v>2.203895439707709</v>
       </c>
       <c r="V33" t="n">
-        <v>1.456670689590051</v>
+        <v>1.39885138549976</v>
       </c>
       <c r="W33" t="n">
-        <v>2.616653573688074</v>
+        <v>2.509534219868353</v>
       </c>
       <c r="X33" t="n">
-        <v>1.620671602057803</v>
+        <v>1.492564183987716</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.606591617468258</v>
+        <v>1.484823959070962</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.690480273874684</v>
+        <v>1.620488293100948</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.458173668943014</v>
+        <v>1.396110889753559</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.627493020421781</v>
+        <v>1.491523265909513</v>
       </c>
     </row>
   </sheetData>
